--- a/pcb/PickAndPlace.xlsx
+++ b/pcb/PickAndPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB1_2025-08-27" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB1_2025-11-15" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="67">
   <si>
     <t>Designator</t>
   </si>
@@ -115,6 +115,60 @@
     <t>-5.223mm</t>
   </si>
   <si>
+    <t>XSMB</t>
+  </si>
+  <si>
+    <t>XDWF-0910-05P</t>
+  </si>
+  <si>
+    <t>CONN-SMD_XDWF-0910-05P</t>
+  </si>
+  <si>
+    <t>39.751mm</t>
+  </si>
+  <si>
+    <t>-20.955mm</t>
+  </si>
+  <si>
+    <t>37.751mm</t>
+  </si>
+  <si>
+    <t>-19.017mm</t>
+  </si>
+  <si>
+    <t>CH2</t>
+  </si>
+  <si>
+    <t>-11.303mm</t>
+  </si>
+  <si>
+    <t>-12.303mm</t>
+  </si>
+  <si>
+    <t>CH3</t>
+  </si>
+  <si>
+    <t>-5.207mm</t>
+  </si>
+  <si>
+    <t>-6.207mm</t>
+  </si>
+  <si>
+    <t>CH7</t>
+  </si>
+  <si>
+    <t>42.164mm</t>
+  </si>
+  <si>
+    <t>-3.175mm</t>
+  </si>
+  <si>
+    <t>43.164mm</t>
+  </si>
+  <si>
+    <t>-5.113mm</t>
+  </si>
+  <si>
     <t>U1</t>
   </si>
   <si>
@@ -130,52 +184,34 @@
     <t>-11.811mm</t>
   </si>
   <si>
-    <t>14.605mm</t>
+    <t>13.225mm</t>
   </si>
   <si>
     <t>-1.651mm</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>XSMB</t>
-  </si>
-  <si>
-    <t>XDWF-0910-05P</t>
-  </si>
-  <si>
-    <t>CONN-SMD_XDWF-0910-05P</t>
-  </si>
-  <si>
-    <t>39.751mm</t>
-  </si>
-  <si>
-    <t>-20.955mm</t>
-  </si>
-  <si>
-    <t>37.751mm</t>
-  </si>
-  <si>
-    <t>-19.017mm</t>
-  </si>
-  <si>
-    <t>CH2</t>
-  </si>
-  <si>
-    <t>-11.303mm</t>
-  </si>
-  <si>
-    <t>-12.303mm</t>
-  </si>
-  <si>
-    <t>CH3</t>
-  </si>
-  <si>
-    <t>-5.207mm</t>
-  </si>
-  <si>
-    <t>-6.207mm</t>
+    <t>KRATOS_IN</t>
+  </si>
+  <si>
+    <t>Test-Point</t>
+  </si>
+  <si>
+    <t>Test-Point-0.5mm</t>
+  </si>
+  <si>
+    <t>39.798mm</t>
+  </si>
+  <si>
+    <t>-9.314mm</t>
+  </si>
+  <si>
+    <t>CH8</t>
+  </si>
+  <si>
+    <t>36.195mm</t>
+  </si>
+  <si>
+    <t>37.195mm</t>
   </si>
 </sst>
 </file>
@@ -552,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -807,7 +843,7 @@
         <v>40</v>
       </c>
       <c r="J6">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
@@ -816,7 +852,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="N6" t="s">
         <v>35</v>
@@ -824,51 +860,51 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
         <v>42</v>
       </c>
-      <c r="B7" t="s">
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" t="s">
         <v>43</v>
       </c>
-      <c r="C7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" t="s">
-        <v>48</v>
-      </c>
       <c r="J7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M7" t="s">
         <v>22</v>
       </c>
       <c r="N7" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
@@ -880,19 +916,19 @@
         <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
       </c>
       <c r="I8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -912,7 +948,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -921,22 +957,22 @@
         <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H9" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="I9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -945,12 +981,144 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M9" t="s">
         <v>22</v>
       </c>
       <c r="N9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10">
+        <v>18</v>
+      </c>
+      <c r="K10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12">
+        <v>5</v>
+      </c>
+      <c r="K12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12">
+        <v>180</v>
+      </c>
+      <c r="M12" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" t="s">
         <v>15</v>
       </c>
     </row>
